--- a/resource/confussion matrix.xlsx
+++ b/resource/confussion matrix.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f4ed61fe0626ee0/Documents/Skripsi/resource/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_96766634FBDACA52E7B58DBBFE67BE8F7801692F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB6DDDF-8CA4-4FFF-BD88-1847C563816E}"/>
+  <bookViews>
+    <workbookView minimized="1" xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="bagaimana confussion matrixnya " sheetId="1" r:id="rId4"/>
+    <sheet name="bagaimana confussion matrixnya " sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>Confussion Matrix</t>
   </si>
@@ -30,58 +39,37 @@
   <si>
     <t>Nilai Prediksi</t>
   </si>
-  <si>
-    <t>A (Benar)</t>
-  </si>
-  <si>
-    <t>B (Error)</t>
-  </si>
-  <si>
-    <t>C (Error Fatal)</t>
-  </si>
-  <si>
-    <t>D (Error)</t>
-  </si>
-  <si>
-    <t>E (Benar)</t>
-  </si>
-  <si>
-    <t>F (Error)</t>
-  </si>
-  <si>
-    <t>G (Error Fatal)</t>
-  </si>
-  <si>
-    <t>H (Error)</t>
-  </si>
-  <si>
-    <t>I (Benar)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -95,45 +83,69 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -143,22 +155,29 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -173,6 +192,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -184,6 +204,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -192,6 +214,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -200,57 +225,57 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="9" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -440,97 +465,156 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="C2:O10"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="13.75"/>
-    <col customWidth="1" min="7" max="7" width="13.75"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
-      <c r="D4" s="1" t="s">
+    <row r="2" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="3:15" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5">
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
+      <c r="G4" s="10"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="4"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="3:15" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C5" s="4"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="D6" s="9" t="s">
+      <c r="I5" s="4"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="3:15" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C6" s="4"/>
+      <c r="D6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="D7" s="12"/>
-      <c r="E7" s="10" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="3:15" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C7" s="4"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" s="13"/>
-      <c r="E8" s="10" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="3:15" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="C8" s="4"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="D4:E5"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="D6:D8"/>
+    <mergeCell ref="K3:L4"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="K5:K7"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/resource/confussion matrix.xlsx
+++ b/resource/confussion matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2f4ed61fe0626ee0/Documents/Skripsi/resource/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afit\OneDrive\Documents\Skripsi\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_96766634FBDACA52E7B58DBBFE67BE8F7801692F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB6DDDF-8CA4-4FFF-BD88-1847C563816E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB12A439-CFBC-49E7-B26F-03C3DADAD148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bagaimana confussion matrixnya " sheetId="1" r:id="rId1"/>
@@ -475,7 +475,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="C2:O10"/>
+  <dimension ref="C2:O13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="13.77734375" customWidth="1"/>
@@ -551,9 +551,15 @@
       <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="F6" s="3">
+        <v>7</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="K6" s="13"/>
       <c r="L6" s="2"/>
@@ -567,9 +573,15 @@
       <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="K7" s="14"/>
       <c r="L7" s="2"/>
@@ -583,9 +595,15 @@
       <c r="E8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>11</v>
+      </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -605,6 +623,12 @@
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
+    </row>
+    <row r="13" spans="3:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f>SUM(F6:H8)</f>
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
